--- a/exports/subscription_journeys_matrix.xlsx
+++ b/exports/subscription_journeys_matrix.xlsx
@@ -4,20 +4,55 @@
   <sheets>
     <sheet name="Journeys Matrix" sheetId="1" r:id="rId1"/>
     <sheet name="Priority" sheetId="2" r:id="rId2"/>
-    <sheet name="Notes" sheetId="3" r:id="rId3"/>
+    <sheet name="Company Seats" sheetId="3" r:id="rId3"/>
+    <sheet name="Notes" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+  </fonts>
+  <fills count="1">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="52" customWidth="1"/>
+    <col min="4" max="4" width="38" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
@@ -57,22 +92,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Primera suscripcion exitosa</t>
+          <t>Alta individual exitosa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Get Payment Link + Stripe checkout.session.completed</t>
+          <t>Get Payment Link + checkout.session.completed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>StripeCheckoutService -&gt; StripeWebhookFunction -&gt; StripeSubscriptionHandler.HandleCheckoutCompletedAsync -&gt; AccessOrchestrator</t>
+          <t>StripeCheckoutHandler -&gt; StripeCheckoutService -&gt; StripeWebhookFunction -&gt; StripeSubscriptionHandler.HandleCheckoutCompletedAsync -&gt; AccessOrchestrator</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Usuario creado/actualizado, suscripcion vinculada, acceso recomputado</t>
+          <t>Usuario creado o actualizado, StripeCustomerId y StripeSubscriptionId persistidos, acceso recomputado</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -82,19 +117,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Usuario entra con acceso completo</t>
+          <t>Usuario activo con acceso Full</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Primera suscripcion abandonada</t>
+          <t>Alta individual abandonada</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Get Payment Link pero sin completar pago</t>
+          <t>Get Payment Link sin completar pago</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -104,12 +139,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>No hay activacion real</t>
+          <t>No se crea activacion valida</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ManyChat no debe pasar a FULL</t>
+          <t>ManyChat no pasa a FULL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -121,704 +156,512 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Primera suscripcion con pago invalido/no completado</t>
+          <t>Renovacion automatica normal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Checkout no completa exitosamente</t>
+          <t>invoice.paid y/o customer.subscription.updated</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>No se consolida lifecycle</t>
+          <t>StripeWebhookFunction -&gt; StripeSubscriptionHandler -&gt; ApplyReducerAsync -&gt; AccessOrchestrator</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sin proyeccion activa valida</t>
+          <t>Usuario sigue active / paid-through</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ManyChat no cambia a FULL</t>
+          <t>Auto-renew reminders solo si no hay journeys superiores</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sin acceso</t>
+          <t>Continuidad normal</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Renovacion automatica normal mensual</t>
+          <t>Payment recovery inicia</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stripe invoice.paid / customer.subscription.updated segun orden</t>
+          <t>invoice.payment_failed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>StripeWebhookFunction -&gt; StripeSubscriptionHandler -&gt; reducer -&gt; AccessOrchestrator</t>
+          <t>StripeWebhookFunction -&gt; StripeSubscriptionHandler -&gt; ApplyReducerAsync -&gt; BillingRecoveryManyChatNotifier</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sigue active / paid-through</t>
+          <t>Usuario entra a delinquency/recovery; PaymentRecoveryStartedAtUtc se abre</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Timer puede enviar auto-renew reminders 7d, 3d, 1d</t>
+          <t>ManyChat recibe recovery_active y suprime auto-renew / save-before-churn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Continuidad normal</t>
+          <t>Inicia journey de recovery</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Renovacion automatica normal anual</t>
+          <t>Payment method update link</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stripe invoice.paid / customer.subscription.updated</t>
+          <t>POST /api/stripe/subscription/payment-method-update-link</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mismo pipeline reducer</t>
+          <t>CreateStripePaymentMethodUpdateLinkUseCase -&gt; StripeAdminClient</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sigue active / paid-through</t>
+          <t>Sin cambio de lifecycle; se genera portal session segura</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Timer puede enviar auto-renew reminders 30d, 14d, 7d, 1d</t>
+          <t>ManyChat o frontend abre Stripe Customer Portal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Continuidad normal</t>
+          <t>Usuario puede actualizar tarjeta</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Falla cobro recurrente</t>
+          <t>Recovery automatico desde Stripe</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stripe invoice.payment_failed</t>
+          <t>customer.updated despues de actualizar tarjeta</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>StripeWebhookFunction -&gt; StripeSubscriptionHandler -&gt; ApplyReducerAsync -&gt; reducer</t>
+          <t>StripeWebhookFunction -&gt; StripeSubscriptionHandler.HandleCustomerUpdatedAsync -&gt; invoice.pay</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Entra en past_due/grace/payment recovery segun reglas</t>
+          <t>Backend intenta recuperar factura abierta sin depender del return_url</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ManyChat recibe recovery_active; payment recovery suprime otros journeys</t>
+          <t>ManyChat no marca exito aun; espera confirmacion final</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Inicia Payment Recovery</t>
+          <t>Retry automatico disparado</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Reintento ManyChat inicial duplicado</t>
+          <t>Recovery manual fallback</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Stripe reenvia invoice.payment_failed duplicado</t>
+          <t>POST /api/stripe/subscription/retry-payment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Proteccion de idempotencia / dedupe en webhook + reducer path</t>
+          <t>RetryStripeOpenInvoiceUseCase -&gt; StripeAdminClient.RetryOpenInvoiceAsync</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>No cambia episodio si ya estaba activo</t>
+          <t>Solo corre como camino manual/fallback</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>No debe duplicar trigger inicial</t>
+          <t>ManyChat puede recibir estado intermedio si el recovery sigue activo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sigue recovery sin duplicados</t>
+          <t>Se intenta invoice.pay</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Usuario abre actualizacion de metodo de pago</t>
+          <t>Recovery exitoso</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Frontend/ManyChat llama POST /stripe/subscription/payment-method-update-link</t>
+          <t>invoice.paid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CreateStripePaymentMethodUpdateLinkUseCase -&gt; StripeAdminClient.CreatePaymentMethodUpdateSessionAsync</t>
+          <t>StripeWebhookFunction -&gt; StripeSubscriptionHandler -&gt; reducer -&gt; AccessOrchestrator</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No cambia lifecycle local</t>
+          <t>Sale de recovery, vuelve a active, PaymentRecoveryStartedAtUtc se limpia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Se obtiene URL segura de Stripe Customer Portal</t>
+          <t>ManyChat recibe recovered y se apagan reminders de recovery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Usuario puede actualizar tarjeta</t>
+          <t>Suscripcion recuperada</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Error creando portal de Stripe</t>
+          <t>Cancel scheduled</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Falla API Stripe al crear portal session</t>
+          <t>cancel_at_period_end=true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CreateStripePaymentMethodUpdateLinkUseCase</t>
+          <t>CancelSubscriptionAtPeriodEndUseCase -&gt; Stripe -&gt; webhook -&gt; reducer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sin cambio lifecycle</t>
+          <t>Usuario sigue activo hasta CurrentPeriodEndUtc</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Backend responde error; ManyChat puede mostrar 'intenta de nuevo'</t>
+          <t>Save-before-churn reemplaza auto-renew</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sigue en recovery</t>
+          <t>Retencion pre-churn activa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Usuario entra a Stripe pero abandona</t>
+          <t>Checkout company seats</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>No completa update o no vuelve</t>
+          <t>Get Payment Link con planType fleet/company_seat y quantity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No webhook final de recuperacion</t>
+          <t>StripeCheckoutHandler -&gt; StripeCheckoutService -&gt; checkout.session.completed -&gt; StripeSubscriptionHandler</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sigue en recovery local</t>
+          <t>Se crea/actualiza Company y Entitlement; SeatsTotal se inicializa desde Stripe quantity</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ManyChat sigue con recovery y timer diario</t>
+          <t>ManyChat puede recibir notificacion de compra company; no se crean usuarios automaticamente</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sigue recovery</t>
+          <t>Capacidad inicial de seats creada</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Usuario actualiza tarjeta y luego app pide retry</t>
+          <t>Join company exitoso</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>POST /stripe/subscription/retry-payment</t>
+          <t>JoinCompanyFunction con invite valido y seats disponibles</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RetryStripeOpenInvoiceUseCase -&gt; StripeAdminClient.RetryOpenInvoiceAsync</t>
+          <t>JoinCompanyFunction -&gt; CompanyJoinHandler -&gt; reservation + EnsureActiveAsync -&gt; AccessOrchestrator</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Aun no cambia lifecycle por si solo</t>
+          <t>SeatAssignment activo, User.CompanyId / SeatEntitlementId actualizados, SeatsUsed reservado</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ManyChat recibe payment_update_pending_confirmation o payment_retry_failed solo si recovery sigue activo</t>
+          <t>No debe haber doble consumo de invite en reintentos idempotentes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Se intento recuperacion</t>
+          <t>Usuario consume un seat real</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Retry sin invoice abierto</t>
+          <t>Join bloqueado por no seats</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>retry-payment y no hay open invoice</t>
+          <t>Invite aceptado cuando SeatsUsed &gt;= SeatsTotal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RetryStripeOpenInvoiceUseCase</t>
+          <t>CompanyJoinHandler</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sin cambio lifecycle</t>
+          <t>Join falla con no_seats_available</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ManyChat recibe estado operativo pendiente, no recovered</t>
+          <t>ManyChat/cliente pueden mostrar conflicto operativo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Espera webhook/estado real</t>
+          <t>No hay sobreasignacion</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Retry falla o invoice sigue impago</t>
+          <t>Over-capacity tras downgrade</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>retry-payment con intento fallido</t>
+          <t>customer.subscription.updated con quantity menor que SeatsUsed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RetryStripeOpenInvoiceUseCase</t>
+          <t>StripeWebhookFunction -&gt; StripeSubscriptionHandler.ProjectCompanyEntitlement*</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sigue recovery</t>
+          <t>SeatsTotal baja, IsOverCapacity=true, usuarios existentes se conservan</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ManyChat recibe payment_retry_failed; siguen follow-ups</t>
+          <t>Nuevos joins quedan bloqueados</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Recovery continua</t>
+          <t>Estado estable y visible de sobrecapacidad</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pago recuperado exitosamente</t>
+          <t>Sync continuo de seats sin user local</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Stripe invoice.paid</t>
+          <t>Evento Stripe de company con User projection ausente pero Company existente</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>StripeWebhookFunction -&gt; StripeSubscriptionHandler -&gt; reducer -&gt; AccessOrchestrator</t>
+          <t>ApplyReducerAsync fallback -&gt; CompanyStore.GetByStripeCustomerIdAsync -&gt; ProjectCompanyEntitlementCoreAsync</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sale de recovery, vuelve a active</t>
+          <t>SeatsTotal y status company siguen sincronizados aunque falte user shadow</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ManyChat recibe recovered; se apagan reminders de recovery</t>
+          <t>No depende de resolver usuario para proyectar entitlement fleet</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Suscripcion recuperada</t>
+          <t>Se evita drift de company seats</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Recovery cerrado sin exito final</t>
+          <t>Company billing delinquent</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Evento Stripe mueve al usuario fuera del episodio sin recuperacion pagada</t>
+          <t>invoice.payment_failed o status past_due para fleet</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>StripeSubscriptionHandler + notifier</t>
+          <t>StripeSubscriptionHandler.ProjectCompanyEntitlementCoreAsync</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PaymentRecoveryStartedAtUtc se limpia</t>
+          <t>Entitlement company pasa a past_due / no activo para joins nuevos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ManyChat recibe closed</t>
+          <t>ManyChat puede seguir recovery del owner si aplica; joins nuevos se bloquean</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Journey de recovery termina</t>
+          <t>Acceso company seguro bajo billing issues</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cancelacion al final de periodo</t>
+          <t>Recount healing</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>API/UX de cancelacion + Stripe update / webhook</t>
+          <t>EntitlementRecountTimer hourly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CancelSubscriptionAtPeriodEndUseCase -&gt; Stripe -&gt; webhook -&gt; reducer</t>
+          <t>EntitlementRecountTimerFunction -&gt; EntitlementRecountService</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>cancel_at_period_end = true, acceso sigue hasta period end</t>
+          <t>SeatsUsed se recalcula desde SeatAssignments activos; IsOverCapacity se corrige</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Save-before-churn reemplaza auto-renew</t>
+          <t>No impacta ManyChat directamente; es healing operacional</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Usuario activo hasta fin de periodo</t>
+          <t>Corrige drift por fallos parciales</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cancel scheduled mensual</t>
+          <t>Subscription deleted fleet</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cancel_at_period_end=true y plan mensual</t>
+          <t>customer.subscription.deleted</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Timer -&gt; SubscriptionReminderService + evaluator</t>
+          <t>StripeWebhookFunction -&gt; StripeSubscriptionHandler.ProjectCompanyEntitlementCoreAsync</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sigue activo hasta end date</t>
+          <t>Entitlement queda paid-through o expired segun EndedAtUtc / CurrentPeriodEndUtc</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Save-before-churn en 7d, 3d, 1d; auto-renew suprimido</t>
+          <t>No nuevos joins cuando ya no este activo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Churn prevention activo</t>
+          <t>Cierre seguro del entitlement company</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cancel scheduled anual</t>
+          <t>Retry / replay de reminders</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cancel_at_period_end=true y plan anual</t>
+          <t>FailedActionRetryService</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Timer -&gt; SubscriptionReminderService + evaluator</t>
+          <t>FailedActionRetryService revalida contra estado actual</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sigue activo hasta end date</t>
+          <t>No reenvia mensajes obsoletos ni journeys contradictorios</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Save-before-churn en 30d, 14d, 7d, 1d; auto-renew suprimido</t>
+          <t>ManyChat recibe solo mensajes vigentes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Churn prevention activo</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Payment recovery mientras cancel scheduled</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Recovery + cancel_at_period_end=true</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Prioridad en SubscriptionReminderService</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Recovery sigue teniendo prioridad</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Solo payment recovery; save-before-churn y auto-renew suprimidos</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Sin mensajes contradictorios</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Fin real del periodo cancelado</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Stripe customer.subscription.deleted o evento final equivalente</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>StripeWebhookFunction -&gt; StripeSubscriptionHandler -&gt; reducer</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Estado final ended/deleted</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>No mas auto-renew, no save-before-churn, no recovery</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Acceso termina correctamente</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Eliminacion final de suscripcion</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Stripe customer.subscription.deleted</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Mismo pipeline</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Estado terminal</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>ManyChat no debe recibir journeys activos</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Suscripcion cerrada</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Evento fuera de orden</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Webhook viejo llega tarde</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>ApplyReducerAsync con out-of-order protection</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Se ignora</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>No mensajes contradictorios</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Estado actual preservado</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Reintento/replay de recordatorio viejo</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Retry store procesa accion vieja</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>FailedActionRetryService</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Revalida contra estado local actual</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Se suprime si ya no aplica o si un journey superior gano</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>No hay dual-send</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Reconciliacion / verificacion posterior</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Servicio de reconciliacion consulta Stripe</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>StripeReconciliationService</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Reproyecta si encuentra diferencias</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ManyChat/acceso se corrigen por estado real</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Consistencia eventual segura</t>
+          <t>Mensajeria consistente</t>
         </is>
       </c>
     </row>
@@ -877,7 +720,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Usuario en past_due/grace/payment recovery segun webhook + reducer</t>
+          <t>Usuario en recovery/delinquency segun webhook + reducer</t>
         </is>
       </c>
     </row>
@@ -899,7 +742,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>cancel_at_period_end = true y suscripcion aun activa hasta period end</t>
+          <t>cancel_at_period_end=true y suscripcion aun activa hasta period end</t>
         </is>
       </c>
     </row>
@@ -916,12 +759,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>No suprime otros; solo corre si no hay journeys superiores</t>
+          <t>Solo corre si no hay journeys superiores</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Suscripcion activa, auto-renew ON, no recovery, no cancel_at_period_end</t>
+          <t>Suscripcion activa, no recovery, no cancel_at_period_end</t>
         </is>
       </c>
     </row>
@@ -931,94 +774,275 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="88" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="38" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Detalle</t>
+          <t>Regla actual</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Fuente de verdad</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Proteccion implementada</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Source of truth</t>
+          <t>SeatsTotal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stripe webhooks siguen siendo la fuente de verdad del lifecycle.</t>
+          <t>Se sincroniza desde Stripe quantity en checkout, subscription.updated, subscription.deleted, invoice.paid e invoice.payment_failed</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Stripe subscription item quantity</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fallback a snapshot de Stripe si faltan campos en webhook; fallback por Company si falta User projection</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>No depende solo del checkout inicial</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Reducer</t>
+          <t>SeatsUsed</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SubscriptionReducer y ApplyReducerAsync siguen controlando las transiciones.</t>
+          <t>Se incrementa por reserva optimista y se corrige por recount</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SeatAssignments activos + reservation flow</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TryReserveSeatAsync, EnsureActiveAsync, ReleaseSeatReservationAsync, EntitlementRecountTimer hourly</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Puede quedar temporalmente alto tras crash intermedio</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Timers</t>
+          <t>Seat availability</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Los timers leen estado proyectado local; no derivan verdad de ManyChat.</t>
+          <t>Join solo si entitlement activo, no over-capacity y hay cupo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Entitlement + SeatAssignments</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CompanyJoinHandler bloquea no_seats_available y company_over_capacity</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>No se crean usuarios desde Stripe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ManyChat</t>
+          <t>Over-capacity</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ManyChat comunica estados y journeys, pero no decide el lifecycle.</t>
+          <t>Se detecta cuando SeatsUsed &gt; SeatsTotal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Entitlement projection + recount</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Nuevos joins bloqueados; usuarios existentes se conservan</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>No hay borrado silencioso</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alta inicial</t>
+          <t>Invite idempotency</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>El checkout inicial usa card y link para mantener FULL access alineado con confirmacion inmediata.</t>
+          <t>No debe reconsumir invite si ya hay seat activo para ese user/company/entitlement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>JoinCompanyFunction + CompanyJoinHandler</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Chequeo previo de active seat antes de TryConsumeAsync</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Tambien cura user projection incompleta</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Payment recovery self-service</t>
+          <t>Crash healing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>El usuario actualiza tarjeta via Stripe Customer Portal y luego el backend puede intentar invoice.pay; la confirmacion final sigue siendo invoice.paid.</t>
+          <t>Healing por retry idempotente y recount</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Operational timers + idempotent join</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EntitlementRecountTimer cada hora</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sigue existiendo una pequena ventana sin transaccion cross-table</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Payment Recovery</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>customer.updated puede disparar retry automatico de invoice.pay. retry-payment queda como fallback manual. El exito final sigue siendo invoice.paid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Company Seats</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Stripe no crea usuarios. Solo define capacidad comprada. Los usuarios consumen asiento cuando JoinCompanyFunction completa la asignacion activa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Recount</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EntitlementRecountTimer corre cada hora al minuto 00 UTC y corrige SeatsUsed / IsOverCapacity a partir de SeatAssignments activos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Known limitation</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>No existe transaccion atomica entre reserva de seat y persistencia del SeatAssignment. Un crash en esa ventana puede inflar SeatsUsed temporalmente hasta que healing o recount lo corrijan.</t>
         </is>
       </c>
     </row>
